--- a/GATEWAY/A1#111TSFNETXX/TSF_SRL/IATROS/4.2.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111TSFNETXX/TSF_SRL/IATROS/4.2.0/report-checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andrea.buzzino\Documents\FSE\GATEWAY\Accreditamento\Accreditamento Gateway 20260323\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C6B21B-08C5-4A49-B2A4-F232C6D8E8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4323EBBD-4D56-49B0-9E42-A3D4F1D9AC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -2411,15 +2411,6 @@
     <t>subject_application_version: 4.2.0</t>
   </si>
   <si>
-    <t>2026-03-23T16:20:12Z</t>
-  </si>
-  <si>
-    <t>fce0af920d748d421a6980be3a88110d</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.50.4.4.318e3d86b07bceb03e30d34a8340e8db02c9c67ae7e40d0957c0f8ee6123d5be.6498a1a585^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>Accreditamento già eseguito</t>
   </si>
   <si>
@@ -2428,6 +2419,15 @@
   </si>
   <si>
     <t>Al medico compare un dialog box con il messaggio di errore.</t>
+  </si>
+  <si>
+    <t>2026-03-23T16:48:51Z</t>
+  </si>
+  <si>
+    <t>764155dac606369d5cf2dcd385b2de69</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.50.4.4.239d723ac25be476e0bc76dacb443a776c733b56c31d74fe468516a57a514c94.b9b2b3cca6^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -3148,6 +3148,9 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3169,9 +3172,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4657,14 +4657,14 @@
       <c r="W1" s="9"/>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="64" t="s">
+      <c r="B2" s="64"/>
+      <c r="C2" s="65" t="s">
         <v>629</v>
       </c>
-      <c r="D2" s="63"/>
+      <c r="D2" s="64"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -4685,14 +4685,14 @@
       <c r="W2" s="9"/>
     </row>
     <row r="3" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="66"/>
-      <c r="C3" s="71" t="s">
+      <c r="B3" s="67"/>
+      <c r="C3" s="72" t="s">
         <v>630</v>
       </c>
-      <c r="D3" s="63"/>
+      <c r="D3" s="64"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -4713,12 +4713,12 @@
       <c r="W3" s="9"/>
     </row>
     <row r="4" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="71" t="s">
+      <c r="A4" s="68"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="72" t="s">
         <v>631</v>
       </c>
-      <c r="D4" s="63"/>
+      <c r="D4" s="64"/>
       <c r="E4" s="4"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -4740,12 +4740,12 @@
       <c r="W4" s="9"/>
     </row>
     <row r="5" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="69"/>
-      <c r="B5" s="70"/>
-      <c r="C5" s="71" t="s">
+      <c r="A5" s="70"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="72" t="s">
         <v>632</v>
       </c>
-      <c r="D5" s="63"/>
+      <c r="D5" s="64"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -4766,8 +4766,8 @@
       <c r="W5" s="9"/>
     </row>
     <row r="6" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="60"/>
-      <c r="B6" s="61"/>
+      <c r="A6" s="61"/>
+      <c r="B6" s="62"/>
       <c r="C6" s="10"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -5648,8 +5648,8 @@
       <c r="N29" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="O29" s="72" t="s">
-        <v>637</v>
+      <c r="O29" s="60" t="s">
+        <v>634</v>
       </c>
       <c r="P29" s="32" t="s">
         <v>541</v>
@@ -5660,8 +5660,8 @@
       <c r="R29" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="S29" s="72" t="s">
-        <v>638</v>
+      <c r="S29" s="60" t="s">
+        <v>635</v>
       </c>
       <c r="T29" s="32"/>
       <c r="U29" s="33" t="s">
@@ -11732,7 +11732,7 @@
         <v>505</v>
       </c>
       <c r="L191" s="32" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="M191" s="32"/>
       <c r="N191" s="32"/>
@@ -11775,7 +11775,7 @@
         <v>505</v>
       </c>
       <c r="L192" s="32" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="M192" s="32"/>
       <c r="N192" s="32"/>
@@ -11811,13 +11811,13 @@
         <v>46104</v>
       </c>
       <c r="G193" s="31" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H193" s="31" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="I193" s="36" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="J193" s="32" t="s">
         <v>75</v>
@@ -19781,6 +19781,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="58b13f75919cba2dcad85f84b1d5db00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3b16ea44285e6579c272a3325f660d0" ns2:_="" ns3:_="">
     <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
@@ -20044,42 +20065,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD72871-87C6-44C4-AEDE-C35BE2C233EE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -20102,9 +20091,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD72871-87C6-44C4-AEDE-C35BE2C233EE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
